--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481268</v>
       </c>
       <c r="B3" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136481269</v>
       </c>
       <c r="B4" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136583117</v>
       </c>
       <c r="B5" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136481018</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136481019</v>
       </c>
       <c r="B7" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481020</v>
       </c>
       <c r="B8" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481259</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136583122</v>
       </c>
       <c r="B10" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136583119</v>
       </c>
       <c r="B11" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>136583121</v>
       </c>
       <c r="B12" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481268</v>
       </c>
       <c r="B3" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136481269</v>
       </c>
       <c r="B4" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136583117</v>
       </c>
       <c r="B5" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136481018</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136481019</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481020</v>
       </c>
       <c r="B8" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481259</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136583122</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136583119</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>136583121</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1749,10 +1749,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136583119</v>
+        <v>136759880</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,21 +1760,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407134</v>
+        <v>407078</v>
       </c>
       <c r="R11" t="n">
-        <v>6850327</v>
+        <v>6850524</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,12 +1818,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1854,16 +1864,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583119</t>
+          <t>https://artportalen.se/Sighting/136759880</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136583121</v>
+        <v>136759882</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,21 +1881,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1899,13 +1909,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407139</v>
+        <v>406974</v>
       </c>
       <c r="R12" t="n">
-        <v>6850207</v>
+        <v>6850570</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,12 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1965,16 +1985,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583121</t>
+          <t>https://artportalen.se/Sighting/136759882</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136583124</v>
+        <v>136583119</v>
       </c>
       <c r="B13" t="n">
-        <v>78877</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,21 +2002,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2010,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407104</v>
+        <v>407134</v>
       </c>
       <c r="R13" t="n">
-        <v>6850329</v>
+        <v>6850327</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,16 +2096,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583124</t>
+          <t>https://artportalen.se/Sighting/136583119</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136583123</v>
+        <v>136583121</v>
       </c>
       <c r="B14" t="n">
-        <v>79231</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,21 +2113,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2121,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407104</v>
+        <v>407139</v>
       </c>
       <c r="R14" t="n">
-        <v>6850329</v>
+        <v>6850207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,16 +2207,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583123</t>
+          <t>https://artportalen.se/Sighting/136583121</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136583120</v>
+        <v>136583124</v>
       </c>
       <c r="B15" t="n">
-        <v>79232</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2232,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407200</v>
+        <v>407104</v>
       </c>
       <c r="R15" t="n">
-        <v>6850085</v>
+        <v>6850329</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,16 +2318,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583120</t>
+          <t>https://artportalen.se/Sighting/136583124</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136583118</v>
+        <v>136583123</v>
       </c>
       <c r="B16" t="n">
-        <v>80064</v>
+        <v>79231</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2335,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2343,7 +2363,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407107</v>
+        <v>407104</v>
       </c>
       <c r="R16" t="n">
         <v>6850329</v>
@@ -2408,6 +2428,228 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583123</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136583120</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>407200</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6850085</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583120</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136583118</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80064</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>407107</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6850329</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136583118</t>
         </is>
@@ -2430,6 +2672,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481268</v>
       </c>
       <c r="B3" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136481269</v>
       </c>
       <c r="B4" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136583117</v>
       </c>
       <c r="B5" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136481018</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136481019</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481020</v>
       </c>
       <c r="B8" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481259</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136583122</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136759880</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>136759882</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>136583119</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>136583121</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>136583124</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136583123</v>
       </c>
       <c r="B16" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>136583120</v>
       </c>
       <c r="B17" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136583118</v>
       </c>
       <c r="B18" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481268</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136481269</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136583117</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136481018</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136481019</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481020</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481259</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136583122</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136759880</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>136759882</v>
       </c>
       <c r="B12" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>136583119</v>
       </c>
       <c r="B13" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>136583121</v>
       </c>
       <c r="B14" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79571</v>
+        <v>79575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81458</v>
+        <v>81462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136481268</v>
       </c>
       <c r="B23" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136481269</v>
       </c>
       <c r="B24" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136583117</v>
       </c>
       <c r="B25" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>136481018</v>
       </c>
       <c r="B27" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>136481019</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136481020</v>
       </c>
       <c r="B29" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136481259</v>
       </c>
       <c r="B30" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>136583122</v>
       </c>
       <c r="B31" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>136583119</v>
       </c>
       <c r="B44" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>136583121</v>
       </c>
       <c r="B45" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136583124</v>
       </c>
       <c r="B52" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>136583123</v>
       </c>
       <c r="B55" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>136583120</v>
       </c>
       <c r="B80" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>136583118</v>
       </c>
       <c r="B88" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>136993397</v>
       </c>
       <c r="B89" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>136993416</v>
       </c>
       <c r="B90" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>136993423</v>
       </c>
       <c r="B91" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>136993458</v>
       </c>
       <c r="B92" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79575</v>
+        <v>79577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81462</v>
+        <v>81464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136481268</v>
       </c>
       <c r="B23" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136481269</v>
       </c>
       <c r="B24" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136583117</v>
       </c>
       <c r="B25" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>136481018</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>136481019</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136481020</v>
       </c>
       <c r="B29" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136481259</v>
       </c>
       <c r="B30" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>136583122</v>
       </c>
       <c r="B31" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>136583119</v>
       </c>
       <c r="B44" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>136583121</v>
       </c>
       <c r="B45" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136583124</v>
       </c>
       <c r="B52" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>136583123</v>
       </c>
       <c r="B55" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>136583120</v>
       </c>
       <c r="B80" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>136583118</v>
       </c>
       <c r="B88" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>136993397</v>
       </c>
       <c r="B89" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>136993416</v>
       </c>
       <c r="B90" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>136993423</v>
       </c>
       <c r="B91" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>136993458</v>
       </c>
       <c r="B92" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79577</v>
+        <v>79578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81464</v>
+        <v>81465</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136481268</v>
       </c>
       <c r="B23" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136481269</v>
       </c>
       <c r="B24" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136583117</v>
       </c>
       <c r="B25" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>136481018</v>
       </c>
       <c r="B27" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>136481019</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136481020</v>
       </c>
       <c r="B29" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136481259</v>
       </c>
       <c r="B30" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>136583122</v>
       </c>
       <c r="B31" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>136583119</v>
       </c>
       <c r="B44" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>136583121</v>
       </c>
       <c r="B45" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136583124</v>
       </c>
       <c r="B52" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>136583123</v>
       </c>
       <c r="B55" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>136583120</v>
       </c>
       <c r="B80" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>136583118</v>
       </c>
       <c r="B88" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>136993397</v>
       </c>
       <c r="B89" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>136993416</v>
       </c>
       <c r="B90" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>136993423</v>
       </c>
       <c r="B91" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>136993458</v>
       </c>
       <c r="B92" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136481268</v>
       </c>
       <c r="B23" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136481269</v>
       </c>
       <c r="B24" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136583117</v>
       </c>
       <c r="B25" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>136481018</v>
       </c>
       <c r="B27" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>136481019</v>
       </c>
       <c r="B28" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136481020</v>
       </c>
       <c r="B29" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136481259</v>
       </c>
       <c r="B30" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>136583122</v>
       </c>
       <c r="B31" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>136583119</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>136583121</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ92"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79578</v>
+        <v>79580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81465</v>
+        <v>81467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136481268</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136481269</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136583117</v>
       </c>
       <c r="B25" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>136481018</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>136481019</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136481020</v>
       </c>
       <c r="B29" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>136481259</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>136583122</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>136583119</v>
       </c>
       <c r="B44" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>136583121</v>
       </c>
       <c r="B45" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136583124</v>
       </c>
       <c r="B52" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>136583123</v>
       </c>
       <c r="B55" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>136583120</v>
       </c>
       <c r="B80" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10401,10 +10401,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136583118</v>
+        <v>137153247</v>
       </c>
       <c r="B88" t="n">
-        <v>80073</v>
+        <v>79243</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10412,21 +10412,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407107</v>
+        <v>407176</v>
       </c>
       <c r="R88" t="n">
-        <v>6850329</v>
+        <v>6850612</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10470,12 +10470,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10506,16 +10506,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583118</t>
+          <t>https://artportalen.se/Sighting/137153247</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136993397</v>
+        <v>136583118</v>
       </c>
       <c r="B89" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10540,17 +10540,21 @@
           <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Dyvelblästan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407188</v>
+        <v>407107</v>
       </c>
       <c r="R89" t="n">
-        <v>6849970</v>
+        <v>6850329</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10577,22 +10581,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10607,27 +10606,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993397</t>
+          <t>https://artportalen.se/Sighting/136583118</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136993416</v>
+        <v>136993397</v>
       </c>
       <c r="B90" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10659,10 +10658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407117</v>
+        <v>407188</v>
       </c>
       <c r="R90" t="n">
-        <v>6850111</v>
+        <v>6849970</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10694,7 +10693,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10704,7 +10703,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10730,16 +10729,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993416</t>
+          <t>https://artportalen.se/Sighting/136993397</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136993423</v>
+        <v>136993416</v>
       </c>
       <c r="B91" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10771,10 +10770,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407099</v>
+        <v>407117</v>
       </c>
       <c r="R91" t="n">
-        <v>6850193</v>
+        <v>6850111</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10806,7 +10805,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10816,7 +10815,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10842,16 +10841,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993423</t>
+          <t>https://artportalen.se/Sighting/136993416</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136993458</v>
+        <v>136993423</v>
       </c>
       <c r="B92" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10883,10 +10882,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407026</v>
+        <v>407099</v>
       </c>
       <c r="R92" t="n">
-        <v>6850890</v>
+        <v>6850193</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10918,7 +10917,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10928,7 +10927,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10953,6 +10952,118 @@
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993423</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>136993458</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>407026</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6850890</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136993458</t>
         </is>
@@ -11051,6 +11162,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81467</v>
+        <v>81457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136583117</v>
       </c>
       <c r="B25" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>136583122</v>
       </c>
       <c r="B31" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>136583119</v>
       </c>
       <c r="B44" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>136583121</v>
       </c>
       <c r="B45" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136583124</v>
       </c>
       <c r="B52" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>136583123</v>
       </c>
       <c r="B55" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>136583120</v>
       </c>
       <c r="B80" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>137153247</v>
       </c>
       <c r="B88" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>136583118</v>
       </c>
       <c r="B89" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>136993397</v>
       </c>
       <c r="B90" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>136993416</v>
       </c>
       <c r="B91" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>136993423</v>
       </c>
       <c r="B92" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>136993458</v>
       </c>
       <c r="B93" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79583</v>
+        <v>79596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81457</v>
+        <v>81470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>136993503</v>
       </c>
       <c r="B73" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136993490</v>
       </c>
       <c r="B74" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>136993409</v>
       </c>
       <c r="B75" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136993447</v>
       </c>
       <c r="B76" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>137153247</v>
       </c>
       <c r="B88" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>136993397</v>
       </c>
       <c r="B90" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>136993416</v>
       </c>
       <c r="B91" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>136993423</v>
       </c>
       <c r="B92" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>136993458</v>
       </c>
       <c r="B93" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79596</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81470</v>
+        <v>81472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>136993503</v>
       </c>
       <c r="B73" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136993490</v>
       </c>
       <c r="B74" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>136993409</v>
       </c>
       <c r="B75" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136993447</v>
       </c>
       <c r="B76" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>137153247</v>
       </c>
       <c r="B88" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>136993397</v>
       </c>
       <c r="B90" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>136993416</v>
       </c>
       <c r="B91" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>136993423</v>
       </c>
       <c r="B92" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>136993458</v>
       </c>
       <c r="B93" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -8736,11 +8736,7 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
@@ -8853,11 +8849,7 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>136993503</v>
       </c>
       <c r="B73" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>136993490</v>
       </c>
       <c r="B74" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136993409</v>
       </c>
       <c r="B75" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>136993447</v>
       </c>
       <c r="B76" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>137153247</v>
       </c>
       <c r="B88" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>136993397</v>
       </c>
       <c r="B90" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>136993416</v>
       </c>
       <c r="B91" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136993423</v>
       </c>
       <c r="B92" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>136993458</v>
       </c>
       <c r="B93" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136759880</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>136759882</v>
       </c>
       <c r="B33" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>79611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>136993503</v>
       </c>
       <c r="B73" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>136993490</v>
       </c>
       <c r="B74" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136993409</v>
       </c>
       <c r="B75" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>136993447</v>
       </c>
       <c r="B76" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>137153247</v>
       </c>
       <c r="B88" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>136993397</v>
       </c>
       <c r="B90" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>136993416</v>
       </c>
       <c r="B91" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136993423</v>
       </c>
       <c r="B92" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>136993458</v>
       </c>
       <c r="B93" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993405</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993414</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993428</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993429</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993438</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993439</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993441</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993452</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993459</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993493</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993442</v>
       </c>
       <c r="B13" t="n">
-        <v>79611</v>
+        <v>79616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136993450</v>
       </c>
       <c r="B14" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993403</v>
       </c>
       <c r="B15" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993427</v>
       </c>
       <c r="B16" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993448</v>
       </c>
       <c r="B17" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993453</v>
       </c>
       <c r="B18" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993467</v>
       </c>
       <c r="B19" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993433</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136993471</v>
       </c>
       <c r="B21" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>136993419</v>
       </c>
       <c r="B26" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>136993417</v>
       </c>
       <c r="B34" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>136993444</v>
       </c>
       <c r="B35" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>136993445</v>
       </c>
       <c r="B36" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>136993446</v>
       </c>
       <c r="B37" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>136993494</v>
       </c>
       <c r="B38" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993401</v>
       </c>
       <c r="B39" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993415</v>
       </c>
       <c r="B40" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993418</v>
       </c>
       <c r="B41" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993420</v>
       </c>
       <c r="B42" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993443</v>
       </c>
       <c r="B43" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>136993464</v>
       </c>
       <c r="B46" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>136993440</v>
       </c>
       <c r="B47" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136993454</v>
       </c>
       <c r="B48" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136993499</v>
       </c>
       <c r="B49" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>136993498</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>136993505</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136993424</v>
       </c>
       <c r="B53" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>136993469</v>
       </c>
       <c r="B54" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>136993413</v>
       </c>
       <c r="B56" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>136993451</v>
       </c>
       <c r="B57" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136993463</v>
       </c>
       <c r="B58" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>136993396</v>
       </c>
       <c r="B59" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>136993404</v>
       </c>
       <c r="B60" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>136993407</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>136993408</v>
       </c>
       <c r="B62" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>136993410</v>
       </c>
       <c r="B63" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>136993426</v>
       </c>
       <c r="B64" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>136993432</v>
       </c>
       <c r="B65" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136993435</v>
       </c>
       <c r="B66" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136993449</v>
       </c>
       <c r="B67" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>136993461</v>
       </c>
       <c r="B68" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>136993472</v>
       </c>
       <c r="B69" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>136993492</v>
       </c>
       <c r="B70" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>136993495</v>
       </c>
       <c r="B71" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136993501</v>
       </c>
       <c r="B72" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>136993503</v>
       </c>
       <c r="B73" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>136993490</v>
       </c>
       <c r="B74" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136993409</v>
       </c>
       <c r="B75" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>136993447</v>
       </c>
       <c r="B76" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136993466</v>
       </c>
       <c r="B77" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>136993468</v>
       </c>
       <c r="B78" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>136993470</v>
       </c>
       <c r="B79" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>136993399</v>
       </c>
       <c r="B81" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>136993421</v>
       </c>
       <c r="B82" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136993437</v>
       </c>
       <c r="B83" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136993455</v>
       </c>
       <c r="B84" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>136993496</v>
       </c>
       <c r="B85" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>136993497</v>
       </c>
       <c r="B86" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>136993502</v>
       </c>
       <c r="B87" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>137153247</v>
       </c>
       <c r="B88" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>136993397</v>
       </c>
       <c r="B90" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>136993416</v>
       </c>
       <c r="B91" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136993423</v>
       </c>
       <c r="B92" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>136993458</v>
       </c>
       <c r="B93" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137405321</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993405</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993414</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993428</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993429</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993438</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993439</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993441</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993452</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993459</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993493</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137405342</v>
       </c>
       <c r="B14" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993442</v>
       </c>
       <c r="B15" t="n">
-        <v>79616</v>
+        <v>79627</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993450</v>
       </c>
       <c r="B16" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993403</v>
       </c>
       <c r="B17" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993427</v>
       </c>
       <c r="B18" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993448</v>
       </c>
       <c r="B19" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993453</v>
       </c>
       <c r="B20" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137405339</v>
       </c>
       <c r="B21" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137405370</v>
       </c>
       <c r="B22" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136993467</v>
       </c>
       <c r="B23" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136993433</v>
       </c>
       <c r="B24" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136993471</v>
       </c>
       <c r="B25" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136993419</v>
       </c>
       <c r="B30" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>137405368</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993417</v>
       </c>
       <c r="B39" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993444</v>
       </c>
       <c r="B40" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993445</v>
       </c>
       <c r="B41" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993446</v>
       </c>
       <c r="B42" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993494</v>
       </c>
       <c r="B43" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>137405332</v>
       </c>
       <c r="B44" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>137405333</v>
       </c>
       <c r="B45" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>137405338</v>
       </c>
       <c r="B46" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>137405340</v>
       </c>
       <c r="B47" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>137405341</v>
       </c>
       <c r="B48" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>137405357</v>
       </c>
       <c r="B49" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>137405358</v>
       </c>
       <c r="B50" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>137405360</v>
       </c>
       <c r="B51" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137405363</v>
       </c>
       <c r="B52" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>137405364</v>
       </c>
       <c r="B53" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>137405369</v>
       </c>
       <c r="B54" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>137405376</v>
       </c>
       <c r="B55" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>136993401</v>
       </c>
       <c r="B56" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136993415</v>
       </c>
       <c r="B57" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>136993418</v>
       </c>
       <c r="B58" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>136993420</v>
       </c>
       <c r="B59" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>136993443</v>
       </c>
       <c r="B60" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136993464</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>136993440</v>
       </c>
       <c r="B64" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>136993454</v>
       </c>
       <c r="B65" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>137405334</v>
       </c>
       <c r="B66" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>137405371</v>
       </c>
       <c r="B67" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136993499</v>
       </c>
       <c r="B68" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>136993498</v>
       </c>
       <c r="B69" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>136993505</v>
       </c>
       <c r="B70" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137405322</v>
       </c>
       <c r="B71" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>137405323</v>
       </c>
       <c r="B72" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>137405325</v>
       </c>
       <c r="B73" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137405336</v>
       </c>
       <c r="B74" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>137405362</v>
       </c>
       <c r="B75" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>136993424</v>
       </c>
       <c r="B77" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>136993469</v>
       </c>
       <c r="B78" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>137405326</v>
       </c>
       <c r="B79" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>136993413</v>
       </c>
       <c r="B81" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>136993451</v>
       </c>
       <c r="B82" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>136993463</v>
       </c>
       <c r="B83" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137405373</v>
       </c>
       <c r="B84" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>136993396</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>136993404</v>
       </c>
       <c r="B86" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>136993407</v>
       </c>
       <c r="B87" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>136993408</v>
       </c>
       <c r="B88" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>136993410</v>
       </c>
       <c r="B89" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>136993426</v>
       </c>
       <c r="B90" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>136993432</v>
       </c>
       <c r="B91" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136993435</v>
       </c>
       <c r="B92" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>136993449</v>
       </c>
       <c r="B93" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>136993461</v>
       </c>
       <c r="B94" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>136993472</v>
       </c>
       <c r="B95" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>136993492</v>
       </c>
       <c r="B96" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>136993495</v>
       </c>
       <c r="B97" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>136993501</v>
       </c>
       <c r="B98" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137405328</v>
       </c>
       <c r="B99" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>137405343</v>
       </c>
       <c r="B100" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>137405366</v>
       </c>
       <c r="B101" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>137405379</v>
       </c>
       <c r="B102" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>137405365</v>
       </c>
       <c r="B103" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>137405374</v>
       </c>
       <c r="B104" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>137405375</v>
       </c>
       <c r="B105" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>136993466</v>
       </c>
       <c r="B111" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>136993468</v>
       </c>
       <c r="B112" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>136993470</v>
       </c>
       <c r="B113" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136993399</v>
       </c>
       <c r="B115" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136993421</v>
       </c>
       <c r="B116" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136993437</v>
       </c>
       <c r="B117" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136993455</v>
       </c>
       <c r="B118" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>136993496</v>
       </c>
       <c r="B119" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>136993497</v>
       </c>
       <c r="B120" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>136993502</v>
       </c>
       <c r="B121" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>137153247</v>
       </c>
       <c r="B122" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>137405359</v>
       </c>
       <c r="B123" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>137405372</v>
       </c>
       <c r="B124" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>136993397</v>
       </c>
       <c r="B126" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136993416</v>
       </c>
       <c r="B127" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136993423</v>
       </c>
       <c r="B128" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>136993458</v>
       </c>
       <c r="B129" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>137405327</v>
       </c>
       <c r="B130" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>137405378</v>
       </c>
       <c r="B131" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>137405335</v>
       </c>
       <c r="B132" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>137405319</v>
       </c>
       <c r="B133" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>137405320</v>
       </c>
       <c r="B134" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>137405324</v>
       </c>
       <c r="B135" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>137405329</v>
       </c>
       <c r="B136" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>137405330</v>
       </c>
       <c r="B137" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>137405331</v>
       </c>
       <c r="B138" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>137405361</v>
       </c>
       <c r="B139" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>137405377</v>
       </c>
       <c r="B140" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137405321</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993405</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993414</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993428</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993429</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993438</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993439</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993441</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993452</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993459</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993493</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137405342</v>
       </c>
       <c r="B14" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993442</v>
       </c>
       <c r="B15" t="n">
-        <v>79627</v>
+        <v>79628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993450</v>
       </c>
       <c r="B16" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993403</v>
       </c>
       <c r="B17" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993427</v>
       </c>
       <c r="B18" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993448</v>
       </c>
       <c r="B19" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993453</v>
       </c>
       <c r="B20" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137405339</v>
       </c>
       <c r="B21" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137405370</v>
       </c>
       <c r="B22" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136993467</v>
       </c>
       <c r="B23" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136993433</v>
       </c>
       <c r="B24" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136993471</v>
       </c>
       <c r="B25" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136993419</v>
       </c>
       <c r="B30" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>137405368</v>
       </c>
       <c r="B31" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993417</v>
       </c>
       <c r="B39" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993444</v>
       </c>
       <c r="B40" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993445</v>
       </c>
       <c r="B41" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993446</v>
       </c>
       <c r="B42" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993494</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>137405332</v>
       </c>
       <c r="B44" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>137405333</v>
       </c>
       <c r="B45" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>137405338</v>
       </c>
       <c r="B46" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>137405340</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>137405341</v>
       </c>
       <c r="B48" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>137405357</v>
       </c>
       <c r="B49" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>137405358</v>
       </c>
       <c r="B50" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>137405360</v>
       </c>
       <c r="B51" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137405363</v>
       </c>
       <c r="B52" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>137405364</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>137405369</v>
       </c>
       <c r="B54" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>137405376</v>
       </c>
       <c r="B55" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>136993401</v>
       </c>
       <c r="B56" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136993415</v>
       </c>
       <c r="B57" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>136993418</v>
       </c>
       <c r="B58" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>136993420</v>
       </c>
       <c r="B59" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>136993443</v>
       </c>
       <c r="B60" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136993464</v>
       </c>
       <c r="B63" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>136993440</v>
       </c>
       <c r="B64" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>136993454</v>
       </c>
       <c r="B65" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>137405334</v>
       </c>
       <c r="B66" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>137405371</v>
       </c>
       <c r="B67" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136993499</v>
       </c>
       <c r="B68" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>136993498</v>
       </c>
       <c r="B69" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>136993505</v>
       </c>
       <c r="B70" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137405322</v>
       </c>
       <c r="B71" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>137405323</v>
       </c>
       <c r="B72" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>137405325</v>
       </c>
       <c r="B73" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137405336</v>
       </c>
       <c r="B74" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>137405362</v>
       </c>
       <c r="B75" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>136993424</v>
       </c>
       <c r="B77" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>136993469</v>
       </c>
       <c r="B78" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>137405326</v>
       </c>
       <c r="B79" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>136993413</v>
       </c>
       <c r="B81" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>136993451</v>
       </c>
       <c r="B82" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>136993463</v>
       </c>
       <c r="B83" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137405373</v>
       </c>
       <c r="B84" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>136993396</v>
       </c>
       <c r="B85" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>136993404</v>
       </c>
       <c r="B86" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>136993407</v>
       </c>
       <c r="B87" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>136993408</v>
       </c>
       <c r="B88" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>136993410</v>
       </c>
       <c r="B89" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>136993426</v>
       </c>
       <c r="B90" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>136993432</v>
       </c>
       <c r="B91" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136993435</v>
       </c>
       <c r="B92" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>136993449</v>
       </c>
       <c r="B93" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>136993461</v>
       </c>
       <c r="B94" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>136993472</v>
       </c>
       <c r="B95" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>136993492</v>
       </c>
       <c r="B96" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>136993495</v>
       </c>
       <c r="B97" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>136993501</v>
       </c>
       <c r="B98" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137405328</v>
       </c>
       <c r="B99" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>137405343</v>
       </c>
       <c r="B100" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>137405366</v>
       </c>
       <c r="B101" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>137405379</v>
       </c>
       <c r="B102" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>137405365</v>
       </c>
       <c r="B103" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>137405374</v>
       </c>
       <c r="B104" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>137405375</v>
       </c>
       <c r="B105" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>136993466</v>
       </c>
       <c r="B111" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>136993468</v>
       </c>
       <c r="B112" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>136993470</v>
       </c>
       <c r="B113" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136993399</v>
       </c>
       <c r="B115" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136993421</v>
       </c>
       <c r="B116" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136993437</v>
       </c>
       <c r="B117" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136993455</v>
       </c>
       <c r="B118" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>136993496</v>
       </c>
       <c r="B119" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>136993497</v>
       </c>
       <c r="B120" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>136993502</v>
       </c>
       <c r="B121" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>137153247</v>
       </c>
       <c r="B122" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>137405359</v>
       </c>
       <c r="B123" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>137405372</v>
       </c>
       <c r="B124" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>136993397</v>
       </c>
       <c r="B126" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136993416</v>
       </c>
       <c r="B127" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136993423</v>
       </c>
       <c r="B128" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>136993458</v>
       </c>
       <c r="B129" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>137405327</v>
       </c>
       <c r="B130" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>137405378</v>
       </c>
       <c r="B131" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>137405335</v>
       </c>
       <c r="B132" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>137405319</v>
       </c>
       <c r="B133" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>137405320</v>
       </c>
       <c r="B134" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>137405324</v>
       </c>
       <c r="B135" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>137405329</v>
       </c>
       <c r="B136" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>137405330</v>
       </c>
       <c r="B137" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>137405331</v>
       </c>
       <c r="B138" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>137405361</v>
       </c>
       <c r="B139" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>137405377</v>
       </c>
       <c r="B140" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137405321</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993405</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993414</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993428</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993429</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993438</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993439</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993441</v>
       </c>
       <c r="B10" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993452</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993459</v>
       </c>
       <c r="B12" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993493</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137405342</v>
       </c>
       <c r="B14" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993442</v>
       </c>
       <c r="B15" t="n">
-        <v>79628</v>
+        <v>79630</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993450</v>
       </c>
       <c r="B16" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993403</v>
       </c>
       <c r="B17" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993427</v>
       </c>
       <c r="B18" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993448</v>
       </c>
       <c r="B19" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993453</v>
       </c>
       <c r="B20" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137405339</v>
       </c>
       <c r="B21" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137405370</v>
       </c>
       <c r="B22" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136993467</v>
       </c>
       <c r="B23" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136993433</v>
       </c>
       <c r="B24" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136993471</v>
       </c>
       <c r="B25" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136993419</v>
       </c>
       <c r="B30" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>137405368</v>
       </c>
       <c r="B31" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993417</v>
       </c>
       <c r="B39" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993444</v>
       </c>
       <c r="B40" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993445</v>
       </c>
       <c r="B41" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993446</v>
       </c>
       <c r="B42" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993494</v>
       </c>
       <c r="B43" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>137405332</v>
       </c>
       <c r="B44" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>137405333</v>
       </c>
       <c r="B45" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>137405338</v>
       </c>
       <c r="B46" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>137405340</v>
       </c>
       <c r="B47" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>137405341</v>
       </c>
       <c r="B48" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>137405357</v>
       </c>
       <c r="B49" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>137405358</v>
       </c>
       <c r="B50" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>137405360</v>
       </c>
       <c r="B51" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137405363</v>
       </c>
       <c r="B52" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>137405364</v>
       </c>
       <c r="B53" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>137405369</v>
       </c>
       <c r="B54" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>137405376</v>
       </c>
       <c r="B55" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>136993401</v>
       </c>
       <c r="B56" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136993415</v>
       </c>
       <c r="B57" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>136993418</v>
       </c>
       <c r="B58" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>136993420</v>
       </c>
       <c r="B59" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>136993443</v>
       </c>
       <c r="B60" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136993464</v>
       </c>
       <c r="B63" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>136993440</v>
       </c>
       <c r="B64" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>136993454</v>
       </c>
       <c r="B65" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>137405334</v>
       </c>
       <c r="B66" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>137405371</v>
       </c>
       <c r="B67" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136993499</v>
       </c>
       <c r="B68" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>136993498</v>
       </c>
       <c r="B69" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>136993505</v>
       </c>
       <c r="B70" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137405322</v>
       </c>
       <c r="B71" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>137405323</v>
       </c>
       <c r="B72" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>137405325</v>
       </c>
       <c r="B73" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137405336</v>
       </c>
       <c r="B74" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>137405362</v>
       </c>
       <c r="B75" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>136993424</v>
       </c>
       <c r="B77" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>136993469</v>
       </c>
       <c r="B78" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>137405326</v>
       </c>
       <c r="B79" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>136993413</v>
       </c>
       <c r="B81" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>136993451</v>
       </c>
       <c r="B82" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>136993463</v>
       </c>
       <c r="B83" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137405373</v>
       </c>
       <c r="B84" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>136993396</v>
       </c>
       <c r="B85" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>136993404</v>
       </c>
       <c r="B86" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>136993407</v>
       </c>
       <c r="B87" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>136993408</v>
       </c>
       <c r="B88" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>136993410</v>
       </c>
       <c r="B89" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>136993426</v>
       </c>
       <c r="B90" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>136993432</v>
       </c>
       <c r="B91" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136993435</v>
       </c>
       <c r="B92" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>136993449</v>
       </c>
       <c r="B93" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>136993461</v>
       </c>
       <c r="B94" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>136993472</v>
       </c>
       <c r="B95" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>136993492</v>
       </c>
       <c r="B96" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>136993495</v>
       </c>
       <c r="B97" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>136993501</v>
       </c>
       <c r="B98" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137405328</v>
       </c>
       <c r="B99" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>137405343</v>
       </c>
       <c r="B100" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>137405366</v>
       </c>
       <c r="B101" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>137405379</v>
       </c>
       <c r="B102" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>137405365</v>
       </c>
       <c r="B103" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>137405374</v>
       </c>
       <c r="B104" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>137405375</v>
       </c>
       <c r="B105" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>136993466</v>
       </c>
       <c r="B111" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>136993468</v>
       </c>
       <c r="B112" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>136993470</v>
       </c>
       <c r="B113" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136993399</v>
       </c>
       <c r="B115" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136993421</v>
       </c>
       <c r="B116" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136993437</v>
       </c>
       <c r="B117" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136993455</v>
       </c>
       <c r="B118" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>136993496</v>
       </c>
       <c r="B119" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>136993497</v>
       </c>
       <c r="B120" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>136993502</v>
       </c>
       <c r="B121" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>137153247</v>
       </c>
       <c r="B122" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>137405359</v>
       </c>
       <c r="B123" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>137405372</v>
       </c>
       <c r="B124" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>136993397</v>
       </c>
       <c r="B126" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136993416</v>
       </c>
       <c r="B127" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136993423</v>
       </c>
       <c r="B128" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>136993458</v>
       </c>
       <c r="B129" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>137405327</v>
       </c>
       <c r="B130" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>137405378</v>
       </c>
       <c r="B131" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>137405335</v>
       </c>
       <c r="B132" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>137405319</v>
       </c>
       <c r="B133" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>137405320</v>
       </c>
       <c r="B134" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>137405324</v>
       </c>
       <c r="B135" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>137405329</v>
       </c>
       <c r="B136" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>137405330</v>
       </c>
       <c r="B137" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>137405331</v>
       </c>
       <c r="B138" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>137405361</v>
       </c>
       <c r="B139" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>137405377</v>
       </c>
       <c r="B140" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92431</v>
+        <v>92432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993405</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993414</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993428</v>
       </c>
       <c r="B6" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993429</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993438</v>
       </c>
       <c r="B8" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993439</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993441</v>
       </c>
       <c r="B10" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993452</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993459</v>
       </c>
       <c r="B12" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993493</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993442</v>
       </c>
       <c r="B15" t="n">
-        <v>79630</v>
+        <v>79631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993450</v>
       </c>
       <c r="B16" t="n">
-        <v>81504</v>
+        <v>81505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993403</v>
       </c>
       <c r="B17" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993427</v>
       </c>
       <c r="B18" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993448</v>
       </c>
       <c r="B19" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993453</v>
       </c>
       <c r="B20" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136993467</v>
       </c>
       <c r="B23" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136993433</v>
       </c>
       <c r="B24" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136993471</v>
       </c>
       <c r="B25" t="n">
-        <v>96646</v>
+        <v>96647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136993419</v>
       </c>
       <c r="B30" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993417</v>
       </c>
       <c r="B39" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993444</v>
       </c>
       <c r="B40" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993445</v>
       </c>
       <c r="B41" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993446</v>
       </c>
       <c r="B42" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993494</v>
       </c>
       <c r="B43" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>136993401</v>
       </c>
       <c r="B56" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136993415</v>
       </c>
       <c r="B57" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>136993418</v>
       </c>
       <c r="B58" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>136993420</v>
       </c>
       <c r="B59" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>136993443</v>
       </c>
       <c r="B60" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136993464</v>
       </c>
       <c r="B63" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>136993440</v>
       </c>
       <c r="B64" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>136993454</v>
       </c>
       <c r="B65" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136993499</v>
       </c>
       <c r="B68" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>136993498</v>
       </c>
       <c r="B69" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>136993505</v>
       </c>
       <c r="B70" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>136993424</v>
       </c>
       <c r="B77" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>136993469</v>
       </c>
       <c r="B78" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>136993413</v>
       </c>
       <c r="B81" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>136993451</v>
       </c>
       <c r="B82" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>136993463</v>
       </c>
       <c r="B83" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>136993396</v>
       </c>
       <c r="B85" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>136993404</v>
       </c>
       <c r="B86" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>136993407</v>
       </c>
       <c r="B87" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>136993408</v>
       </c>
       <c r="B88" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>136993410</v>
       </c>
       <c r="B89" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>136993426</v>
       </c>
       <c r="B90" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>136993432</v>
       </c>
       <c r="B91" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136993435</v>
       </c>
       <c r="B92" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>136993449</v>
       </c>
       <c r="B93" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>136993461</v>
       </c>
       <c r="B94" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>136993472</v>
       </c>
       <c r="B95" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>136993492</v>
       </c>
       <c r="B96" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>136993495</v>
       </c>
       <c r="B97" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>136993501</v>
       </c>
       <c r="B98" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>136993466</v>
       </c>
       <c r="B111" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>136993468</v>
       </c>
       <c r="B112" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>136993470</v>
       </c>
       <c r="B113" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136993399</v>
       </c>
       <c r="B115" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136993421</v>
       </c>
       <c r="B116" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136993437</v>
       </c>
       <c r="B117" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136993455</v>
       </c>
       <c r="B118" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>136993496</v>
       </c>
       <c r="B119" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>136993497</v>
       </c>
       <c r="B120" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>136993502</v>
       </c>
       <c r="B121" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>136993397</v>
       </c>
       <c r="B126" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136993416</v>
       </c>
       <c r="B127" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136993423</v>
       </c>
       <c r="B128" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>136993458</v>
       </c>
       <c r="B129" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993425</v>
       </c>
       <c r="B2" t="n">
-        <v>92432</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137405321</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993405</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993414</v>
       </c>
       <c r="B5" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993428</v>
       </c>
       <c r="B6" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993429</v>
       </c>
       <c r="B7" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993438</v>
       </c>
       <c r="B8" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993439</v>
       </c>
       <c r="B9" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993441</v>
       </c>
       <c r="B10" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136993452</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136993459</v>
       </c>
       <c r="B12" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136993493</v>
       </c>
       <c r="B13" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137405342</v>
       </c>
       <c r="B14" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136993442</v>
       </c>
       <c r="B15" t="n">
-        <v>79631</v>
+        <v>79634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136993450</v>
       </c>
       <c r="B16" t="n">
-        <v>81505</v>
+        <v>81508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136993403</v>
       </c>
       <c r="B17" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136993427</v>
       </c>
       <c r="B18" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136993448</v>
       </c>
       <c r="B19" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136993453</v>
       </c>
       <c r="B20" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137405339</v>
       </c>
       <c r="B21" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137405370</v>
       </c>
       <c r="B22" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136993467</v>
       </c>
       <c r="B23" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136993433</v>
       </c>
       <c r="B24" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136993471</v>
       </c>
       <c r="B25" t="n">
-        <v>96647</v>
+        <v>96650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136993419</v>
       </c>
       <c r="B30" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>137405368</v>
       </c>
       <c r="B31" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>136993417</v>
       </c>
       <c r="B39" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>136993444</v>
       </c>
       <c r="B40" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>136993445</v>
       </c>
       <c r="B41" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136993446</v>
       </c>
       <c r="B42" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136993494</v>
       </c>
       <c r="B43" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>137405332</v>
       </c>
       <c r="B44" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>137405333</v>
       </c>
       <c r="B45" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>137405338</v>
       </c>
       <c r="B46" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>137405340</v>
       </c>
       <c r="B47" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>137405341</v>
       </c>
       <c r="B48" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>137405357</v>
       </c>
       <c r="B49" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>137405358</v>
       </c>
       <c r="B50" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>137405360</v>
       </c>
       <c r="B51" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137405363</v>
       </c>
       <c r="B52" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>137405364</v>
       </c>
       <c r="B53" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>137405369</v>
       </c>
       <c r="B54" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>137405376</v>
       </c>
       <c r="B55" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>136993401</v>
       </c>
       <c r="B56" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136993415</v>
       </c>
       <c r="B57" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>136993418</v>
       </c>
       <c r="B58" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>136993420</v>
       </c>
       <c r="B59" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>136993443</v>
       </c>
       <c r="B60" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136993464</v>
       </c>
       <c r="B63" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>136993440</v>
       </c>
       <c r="B64" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>136993454</v>
       </c>
       <c r="B65" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>137405334</v>
       </c>
       <c r="B66" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>137405371</v>
       </c>
       <c r="B67" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136993499</v>
       </c>
       <c r="B68" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>136993498</v>
       </c>
       <c r="B69" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>136993505</v>
       </c>
       <c r="B70" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137405322</v>
       </c>
       <c r="B71" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>137405323</v>
       </c>
       <c r="B72" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>137405325</v>
       </c>
       <c r="B73" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137405336</v>
       </c>
       <c r="B74" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>137405362</v>
       </c>
       <c r="B75" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>136993424</v>
       </c>
       <c r="B77" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>136993469</v>
       </c>
       <c r="B78" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>137405326</v>
       </c>
       <c r="B79" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>136993413</v>
       </c>
       <c r="B81" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>136993451</v>
       </c>
       <c r="B82" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>136993463</v>
       </c>
       <c r="B83" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137405373</v>
       </c>
       <c r="B84" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>136993396</v>
       </c>
       <c r="B85" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>136993404</v>
       </c>
       <c r="B86" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>136993407</v>
       </c>
       <c r="B87" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>136993408</v>
       </c>
       <c r="B88" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>136993410</v>
       </c>
       <c r="B89" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>136993426</v>
       </c>
       <c r="B90" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>136993432</v>
       </c>
       <c r="B91" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136993435</v>
       </c>
       <c r="B92" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>136993449</v>
       </c>
       <c r="B93" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>136993461</v>
       </c>
       <c r="B94" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>136993472</v>
       </c>
       <c r="B95" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>136993492</v>
       </c>
       <c r="B96" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>136993495</v>
       </c>
       <c r="B97" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>136993501</v>
       </c>
       <c r="B98" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137405328</v>
       </c>
       <c r="B99" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>137405343</v>
       </c>
       <c r="B100" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>137405366</v>
       </c>
       <c r="B101" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>137405379</v>
       </c>
       <c r="B102" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>137405365</v>
       </c>
       <c r="B103" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>137405374</v>
       </c>
       <c r="B104" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>137405375</v>
       </c>
       <c r="B105" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>136993503</v>
       </c>
       <c r="B106" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>136993490</v>
       </c>
       <c r="B107" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>137405367</v>
       </c>
       <c r="B108" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>136993409</v>
       </c>
       <c r="B109" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>136993447</v>
       </c>
       <c r="B110" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>136993466</v>
       </c>
       <c r="B111" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>136993468</v>
       </c>
       <c r="B112" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>136993470</v>
       </c>
       <c r="B113" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136993399</v>
       </c>
       <c r="B115" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136993421</v>
       </c>
       <c r="B116" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136993437</v>
       </c>
       <c r="B117" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136993455</v>
       </c>
       <c r="B118" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>136993496</v>
       </c>
       <c r="B119" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>136993497</v>
       </c>
       <c r="B120" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>136993502</v>
       </c>
       <c r="B121" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>137153247</v>
       </c>
       <c r="B122" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>137405359</v>
       </c>
       <c r="B123" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>137405372</v>
       </c>
       <c r="B124" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>136993397</v>
       </c>
       <c r="B126" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136993416</v>
       </c>
       <c r="B127" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136993423</v>
       </c>
       <c r="B128" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>136993458</v>
       </c>
       <c r="B129" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>137405327</v>
       </c>
       <c r="B130" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>137405378</v>
       </c>
       <c r="B131" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>137405335</v>
       </c>
       <c r="B132" t="n">
-        <v>93516</v>
+        <v>93520</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>137405319</v>
       </c>
       <c r="B133" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>137405320</v>
       </c>
       <c r="B134" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>137405324</v>
       </c>
       <c r="B135" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>137405329</v>
       </c>
       <c r="B136" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>137405330</v>
       </c>
       <c r="B137" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>137405331</v>
       </c>
       <c r="B138" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>137405361</v>
       </c>
       <c r="B139" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>137405377</v>
       </c>
       <c r="B140" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
